--- a/samples/edge-cases/edge-cover-letter/template.xlsx
+++ b/samples/edge-cases/edge-cover-letter/template.xlsx
@@ -106,12 +106,17 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.3999755851924192"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -145,12 +150,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
@@ -180,7 +186,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -594,38 +600,39 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="6" customFormat="1" customHeight="1" s="3"/>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>〒000-0000</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>発送日</t>
         </is>
       </c>
-      <c r="H3" s="5" t="n">
+      <c r="H3" s="6" t="n">
         <v>46113</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>(住所)</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>文書番号</t>
         </is>
       </c>
-      <c r="H4" s="7" t="n">
+      <c r="H4" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="F5" s="8" t="inlineStr">
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t>(差出人)</t>
         </is>
@@ -633,31 +640,31 @@
     </row>
     <row r="6"/>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>(会社名)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>(部署)</t>
         </is>
       </c>
-      <c r="C8" s="11" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>(担当者名)</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>様</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>拝啓 時下ますますご清栄のこととお慶び申し上げます。平素は格別のお引き立てを賜り、厚く御礼申し上げます。下記の書類をお送りいたしますので、ご査収くださいますようお願い申し上げます。</t>
         </is>
@@ -666,190 +673,190 @@
     <row r="11"/>
     <row r="12"/>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="14" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t>書類名</t>
         </is>
       </c>
-      <c r="C14" s="14" t="n"/>
-      <c r="D14" s="14" t="n"/>
-      <c r="E14" s="14" t="n"/>
-      <c r="F14" s="14" t="n"/>
-      <c r="G14" s="14" t="inlineStr">
+      <c r="C14" s="15" t="n"/>
+      <c r="D14" s="15" t="n"/>
+      <c r="E14" s="15" t="n"/>
+      <c r="F14" s="15" t="n"/>
+      <c r="G14" s="15" t="inlineStr">
         <is>
           <t>部数</t>
         </is>
       </c>
-      <c r="H14" s="14" t="inlineStr">
+      <c r="H14" s="15" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="n">
+      <c r="A15" s="16" t="n">
         <v>1</v>
       </c>
-      <c r="B15" s="16" t="n"/>
-      <c r="C15" s="16" t="n"/>
-      <c r="D15" s="16" t="n"/>
-      <c r="E15" s="16" t="n"/>
-      <c r="F15" s="16" t="n"/>
-      <c r="G15" s="17" t="n"/>
-      <c r="H15" s="18" t="n"/>
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="17" t="n"/>
+      <c r="D15" s="17" t="n"/>
+      <c r="E15" s="17" t="n"/>
+      <c r="F15" s="17" t="n"/>
+      <c r="G15" s="18" t="n"/>
+      <c r="H15" s="19" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="n">
+      <c r="A16" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="B16" s="16" t="n"/>
-      <c r="C16" s="16" t="n"/>
-      <c r="D16" s="16" t="n"/>
-      <c r="E16" s="16" t="n"/>
-      <c r="F16" s="16" t="n"/>
-      <c r="G16" s="17" t="n"/>
-      <c r="H16" s="18" t="n"/>
+      <c r="B16" s="17" t="n"/>
+      <c r="C16" s="17" t="n"/>
+      <c r="D16" s="17" t="n"/>
+      <c r="E16" s="17" t="n"/>
+      <c r="F16" s="17" t="n"/>
+      <c r="G16" s="18" t="n"/>
+      <c r="H16" s="19" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="n">
+      <c r="A17" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="B17" s="16" t="n"/>
-      <c r="C17" s="16" t="n"/>
-      <c r="D17" s="16" t="n"/>
-      <c r="E17" s="16" t="n"/>
-      <c r="F17" s="16" t="n"/>
-      <c r="G17" s="17" t="n"/>
-      <c r="H17" s="18" t="n"/>
+      <c r="B17" s="17" t="n"/>
+      <c r="C17" s="17" t="n"/>
+      <c r="D17" s="17" t="n"/>
+      <c r="E17" s="17" t="n"/>
+      <c r="F17" s="17" t="n"/>
+      <c r="G17" s="18" t="n"/>
+      <c r="H17" s="19" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="n">
+      <c r="A18" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="B18" s="16" t="n"/>
-      <c r="C18" s="16" t="n"/>
-      <c r="D18" s="16" t="n"/>
-      <c r="E18" s="16" t="n"/>
-      <c r="F18" s="16" t="n"/>
-      <c r="G18" s="17" t="n"/>
-      <c r="H18" s="18" t="n"/>
+      <c r="B18" s="17" t="n"/>
+      <c r="C18" s="17" t="n"/>
+      <c r="D18" s="17" t="n"/>
+      <c r="E18" s="17" t="n"/>
+      <c r="F18" s="17" t="n"/>
+      <c r="G18" s="18" t="n"/>
+      <c r="H18" s="19" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="n">
+      <c r="A19" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="B19" s="16" t="n"/>
-      <c r="C19" s="16" t="n"/>
-      <c r="D19" s="16" t="n"/>
-      <c r="E19" s="16" t="n"/>
-      <c r="F19" s="16" t="n"/>
-      <c r="G19" s="17" t="n"/>
-      <c r="H19" s="18" t="n"/>
+      <c r="B19" s="17" t="n"/>
+      <c r="C19" s="17" t="n"/>
+      <c r="D19" s="17" t="n"/>
+      <c r="E19" s="17" t="n"/>
+      <c r="F19" s="17" t="n"/>
+      <c r="G19" s="18" t="n"/>
+      <c r="H19" s="19" t="n"/>
     </row>
     <row r="21">
-      <c r="F21" s="19" t="inlineStr">
+      <c r="F21" s="20" t="inlineStr">
         <is>
           <t>金額(標準)</t>
         </is>
       </c>
-      <c r="G21" s="20" t="n"/>
-      <c r="H21" s="20" t="n"/>
+      <c r="G21" s="21" t="n"/>
+      <c r="H21" s="21" t="n"/>
     </row>
     <row r="22">
-      <c r="F22" s="19" t="inlineStr">
+      <c r="F22" s="20" t="inlineStr">
         <is>
           <t>金額(右揃え)</t>
         </is>
       </c>
-      <c r="G22" s="21" t="n"/>
-      <c r="H22" s="21" t="n"/>
+      <c r="G22" s="22" t="n"/>
+      <c r="H22" s="22" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="22" t="inlineStr">
+      <c r="A24" s="23" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="23" t="n"/>
-      <c r="B25" s="23" t="n"/>
-      <c r="C25" s="23" t="n"/>
-      <c r="D25" s="23" t="n"/>
-      <c r="E25" s="23" t="n"/>
-      <c r="F25" s="23" t="n"/>
-      <c r="G25" s="23" t="n"/>
-      <c r="H25" s="23" t="n"/>
+      <c r="A25" s="24" t="n"/>
+      <c r="B25" s="24" t="n"/>
+      <c r="C25" s="24" t="n"/>
+      <c r="D25" s="24" t="n"/>
+      <c r="E25" s="24" t="n"/>
+      <c r="F25" s="24" t="n"/>
+      <c r="G25" s="24" t="n"/>
+      <c r="H25" s="24" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="23" t="n"/>
-      <c r="B26" s="23" t="n"/>
-      <c r="C26" s="23" t="n"/>
-      <c r="D26" s="23" t="n"/>
-      <c r="E26" s="23" t="n"/>
-      <c r="F26" s="23" t="n"/>
-      <c r="G26" s="23" t="n"/>
-      <c r="H26" s="23" t="n"/>
+      <c r="A26" s="24" t="n"/>
+      <c r="B26" s="24" t="n"/>
+      <c r="C26" s="24" t="n"/>
+      <c r="D26" s="24" t="n"/>
+      <c r="E26" s="24" t="n"/>
+      <c r="F26" s="24" t="n"/>
+      <c r="G26" s="24" t="n"/>
+      <c r="H26" s="24" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="23" t="n"/>
-      <c r="B27" s="23" t="n"/>
-      <c r="C27" s="23" t="n"/>
-      <c r="D27" s="23" t="n"/>
-      <c r="E27" s="23" t="n"/>
-      <c r="F27" s="23" t="n"/>
-      <c r="G27" s="23" t="n"/>
-      <c r="H27" s="23" t="n"/>
+      <c r="A27" s="24" t="n"/>
+      <c r="B27" s="24" t="n"/>
+      <c r="C27" s="24" t="n"/>
+      <c r="D27" s="24" t="n"/>
+      <c r="E27" s="24" t="n"/>
+      <c r="F27" s="24" t="n"/>
+      <c r="G27" s="24" t="n"/>
+      <c r="H27" s="24" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="23" t="n"/>
-      <c r="B28" s="23" t="n"/>
-      <c r="C28" s="23" t="n"/>
-      <c r="D28" s="23" t="n"/>
-      <c r="E28" s="23" t="n"/>
-      <c r="F28" s="23" t="n"/>
-      <c r="G28" s="23" t="n"/>
-      <c r="H28" s="23" t="n"/>
+      <c r="A28" s="24" t="n"/>
+      <c r="B28" s="24" t="n"/>
+      <c r="C28" s="24" t="n"/>
+      <c r="D28" s="24" t="n"/>
+      <c r="E28" s="24" t="n"/>
+      <c r="F28" s="24" t="n"/>
+      <c r="G28" s="24" t="n"/>
+      <c r="H28" s="24" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="23" t="n"/>
-      <c r="B29" s="23" t="n"/>
-      <c r="C29" s="23" t="n"/>
-      <c r="D29" s="23" t="n"/>
-      <c r="E29" s="23" t="n"/>
-      <c r="F29" s="23" t="n"/>
-      <c r="G29" s="23" t="n"/>
-      <c r="H29" s="23" t="n"/>
+      <c r="A29" s="24" t="n"/>
+      <c r="B29" s="24" t="n"/>
+      <c r="C29" s="24" t="n"/>
+      <c r="D29" s="24" t="n"/>
+      <c r="E29" s="24" t="n"/>
+      <c r="F29" s="24" t="n"/>
+      <c r="G29" s="24" t="n"/>
+      <c r="H29" s="24" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="24" t="inlineStr">
+      <c r="A30" s="25" t="inlineStr">
         <is>
           <t>以下は書式の作り方を変えた差し込みセル</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="25" t="inlineStr">
+      <c r="A31" s="26" t="inlineStr">
         <is>
           <t>英字</t>
         </is>
       </c>
-      <c r="B31" s="26" t="inlineStr"/>
+      <c r="B31" s="27" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="25" t="inlineStr">
+      <c r="A32" s="26" t="inlineStr">
         <is>
           <t>未設定</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="25" t="inlineStr">
+      <c r="A33" s="26" t="inlineStr">
         <is>
           <t>列書式</t>
         </is>
